--- a/inst/extdata/Pathway_Embedding.xlsx
+++ b/inst/extdata/Pathway_Embedding.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huangyaqing/Documents/GitHub/FunLearning/PathwayEmbed/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1850F791-6810-B54F-A5D8-366162A82CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA35944F-5CE5-D344-9A0C-86E0054D8AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16940" activeTab="5" xr2:uid="{4F2C48FB-5C4A-5F4C-A80D-28B50AF3CCC3}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16940" activeTab="4" xr2:uid="{4F2C48FB-5C4A-5F4C-A80D-28B50AF3CCC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hippo" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="192">
   <si>
     <t xml:space="preserve">Molecules </t>
   </si>
@@ -180,24 +180,12 @@
     <t>Arnt</t>
   </si>
   <si>
-    <t>p300</t>
-  </si>
-  <si>
-    <t>CBP</t>
-  </si>
-  <si>
-    <t>Phd</t>
-  </si>
-  <si>
     <t>VEGF</t>
   </si>
   <si>
     <t>Glut1</t>
   </si>
   <si>
-    <t>Fih1</t>
-  </si>
-  <si>
     <t>Epo</t>
   </si>
   <si>
@@ -213,13 +201,6 @@
     <t>Cul2</t>
   </si>
   <si>
-    <t>https://www.genome.jp/kegg-bin/show_pathway?map04066</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://
-doi.org/10.1111/cas.13483</t>
-  </si>
-  <si>
     <t>Sirt2</t>
   </si>
   <si>
@@ -635,6 +616,21 @@
   </si>
   <si>
     <t>STRIPAKs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://doi.org/10.1111/cas.13483</t>
+  </si>
+  <si>
+    <t>Nrf1</t>
+  </si>
+  <si>
+    <t>Phd1</t>
+  </si>
+  <si>
+    <t>Phd2</t>
+  </si>
+  <si>
+    <t>Phd3</t>
   </si>
 </sst>
 </file>
@@ -1053,21 +1049,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -1079,7 +1075,7 @@
         <v>-1</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1090,7 +1086,7 @@
         <v>-1</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1101,7 +1097,7 @@
         <v>-1</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1112,7 +1108,7 @@
         <v>-1</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1123,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1136,51 +1132,51 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B10">
         <v>-1</v>
       </c>
       <c r="C10" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B11">
         <v>-1</v>
       </c>
       <c r="C11" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B12">
         <v>-1</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B13">
         <v>-1</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -1188,7 +1184,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -1196,7 +1192,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1204,7 +1200,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1212,7 +1208,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1220,7 +1216,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1228,7 +1224,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -1236,7 +1232,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -1244,7 +1240,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -1252,7 +1248,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -1260,7 +1256,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1268,7 +1264,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -1276,7 +1272,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -1284,7 +1280,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -1292,7 +1288,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -1729,7 +1725,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -1741,7 +1737,7 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1779,51 +1775,51 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -1872,7 +1868,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1899,7 +1895,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1910,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1921,12 +1917,12 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -1934,63 +1930,63 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2025,25 +2021,23 @@
         <v>1</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>188</v>
       </c>
       <c r="B3" s="1">
         <v>-1</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="3" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>189</v>
       </c>
       <c r="B4" s="1">
         <v>-1</v>
@@ -2052,7 +2046,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>190</v>
       </c>
       <c r="B5" s="1">
         <v>-1</v>
@@ -2061,7 +2055,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>191</v>
       </c>
       <c r="B6" s="1">
         <v>-1</v>
@@ -2070,7 +2064,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B7" s="1">
         <v>-1</v>
@@ -2079,7 +2073,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -2088,7 +2082,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -2097,7 +2091,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
@@ -2106,7 +2100,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
@@ -2115,7 +2109,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1">
         <v>-1</v>
@@ -2123,7 +2117,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B13" s="1">
         <v>-1</v>
@@ -2131,7 +2125,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
@@ -2139,7 +2133,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B15" s="1">
         <v>-1</v>
@@ -2147,7 +2141,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
@@ -2155,7 +2149,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B17" s="1">
         <v>-1</v>
@@ -2163,7 +2157,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B18" s="1">
         <v>-1</v>
@@ -2171,7 +2165,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
@@ -2179,16 +2173,13 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{A3353B12-D1B7-9E44-9E19-D3141A685D57}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2211,338 +2202,338 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B5" s="1">
         <v>-1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B6" s="1">
         <v>-1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B22">
         <v>-1</v>
       </c>
       <c r="C22" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B23">
         <v>-1</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B24">
         <v>-1</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B25">
         <v>-1</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B26">
         <v>-1</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B27">
         <v>-1</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B28">
         <v>-1</v>
       </c>
       <c r="C28" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2573,167 +2564,167 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B10" s="1">
         <v>-1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B11" s="1">
         <v>-1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B12" s="1">
         <v>-1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2761,23 +2752,23 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -2785,7 +2776,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2793,7 +2784,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -2801,18 +2792,18 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B6">
         <v>-1</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -2820,7 +2811,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -2828,51 +2819,51 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B11">
         <v>-1</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B12">
         <v>-1</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2880,7 +2871,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -2888,7 +2879,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B15">
         <v>-1</v>
@@ -2896,7 +2887,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B16">
         <v>-1</v>
@@ -2904,7 +2895,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -2936,7 +2927,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -2945,21 +2936,21 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>

--- a/inst/extdata/Pathway_Embedding.xlsx
+++ b/inst/extdata/Pathway_Embedding.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huangyaqing/Documents/GitHub/FunLearning/PathwayEmbed/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huangyaqing/Desktop/GitHub/FunLearning/PathwayEmbed/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA35944F-5CE5-D344-9A0C-86E0054D8AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D600B9BB-3A6A-DD4B-931A-255F0218A6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16940" activeTab="4" xr2:uid="{4F2C48FB-5C4A-5F4C-A80D-28B50AF3CCC3}"/>
+    <workbookView xWindow="12380" yWindow="760" windowWidth="29400" windowHeight="16940" activeTab="4" xr2:uid="{4F2C48FB-5C4A-5F4C-A80D-28B50AF3CCC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hippo" sheetId="1" r:id="rId1"/>
@@ -180,9 +180,6 @@
     <t>Arnt</t>
   </si>
   <si>
-    <t>VEGF</t>
-  </si>
-  <si>
     <t>Glut1</t>
   </si>
   <si>
@@ -631,6 +628,9 @@
   </si>
   <si>
     <t>Phd3</t>
+  </si>
+  <si>
+    <t>Vegfa</t>
   </si>
 </sst>
 </file>
@@ -1049,21 +1049,21 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
         <v>182</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>183</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -1075,7 +1075,7 @@
         <v>-1</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1086,7 +1086,7 @@
         <v>-1</v>
       </c>
       <c r="C5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1097,7 +1097,7 @@
         <v>-1</v>
       </c>
       <c r="C6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1108,7 +1108,7 @@
         <v>-1</v>
       </c>
       <c r="C7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1119,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1132,51 +1132,51 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B10">
         <v>-1</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B11">
         <v>-1</v>
       </c>
       <c r="C11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B12">
         <v>-1</v>
       </c>
       <c r="C12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13">
         <v>-1</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1208,7 +1208,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1216,7 +1216,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -1248,7 +1248,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1264,7 +1264,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -1272,7 +1272,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -1725,7 +1725,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1775,51 +1775,51 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="B9" s="1">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -1868,7 +1868,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1895,7 +1895,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1906,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1917,12 +1917,12 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -1930,63 +1930,63 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
         <v>138</v>
-      </c>
-      <c r="B11" s="1">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
         <v>141</v>
       </c>
-      <c r="B12" s="1">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>142</v>
-      </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="1">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>144</v>
-      </c>
-      <c r="D13" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2025,19 +2025,19 @@
     </row>
     <row r="3" spans="1:4" ht="68" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B3" s="1">
         <v>-1</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B4" s="1">
         <v>-1</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B5" s="1">
         <v>-1</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B6" s="1">
         <v>-1</v>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1">
         <v>-1</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -2091,7 +2091,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>191</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="1">
         <v>-1</v>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="1">
         <v>-1</v>
@@ -2125,7 +2125,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
@@ -2133,7 +2133,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="1">
         <v>-1</v>
@@ -2141,7 +2141,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="1">
         <v>1</v>
@@ -2149,7 +2149,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="1">
         <v>-1</v>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" s="1">
         <v>-1</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="1">
         <v>1</v>
@@ -2173,7 +2173,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
@@ -2202,338 +2202,338 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="1">
+        <v>-1</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B5" s="1">
-        <v>-1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="1">
         <v>-1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22">
         <v>-1</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B23">
         <v>-1</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B24">
         <v>-1</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B25">
         <v>-1</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B26">
         <v>-1</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B27">
         <v>-1</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B28">
         <v>-1</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
         <v>160</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2564,167 +2564,167 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B10" s="1">
         <v>-1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B11" s="1">
         <v>-1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="B12" s="1">
-        <v>-1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B15" s="1">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2752,23 +2752,23 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -2792,18 +2792,18 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B6">
         <v>-1</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -2811,7 +2811,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -2819,51 +2819,51 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11">
+        <v>-1</v>
+      </c>
+      <c r="C11" t="s">
         <v>108</v>
-      </c>
-      <c r="B11">
-        <v>-1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B12">
         <v>-1</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2871,7 +2871,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B15">
         <v>-1</v>
@@ -2887,7 +2887,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B16">
         <v>-1</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -2927,7 +2927,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -2936,21 +2936,21 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>

--- a/inst/extdata/Pathway_Embedding.xlsx
+++ b/inst/extdata/Pathway_Embedding.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huangyaqing/Desktop/GitHub/FunLearning/PathwayEmbed/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D600B9BB-3A6A-DD4B-931A-255F0218A6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59E3956-168F-2C41-9357-9D41ECAE35B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12380" yWindow="760" windowWidth="29400" windowHeight="16940" activeTab="4" xr2:uid="{4F2C48FB-5C4A-5F4C-A80D-28B50AF3CCC3}"/>
+    <workbookView xWindow="14260" yWindow="2740" windowWidth="29400" windowHeight="16940" activeTab="5" xr2:uid="{4F2C48FB-5C4A-5F4C-A80D-28B50AF3CCC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hippo" sheetId="1" r:id="rId1"/>
@@ -22,17 +22,6 @@
     <sheet name="Hedgehog" sheetId="9" r:id="rId7"/>
     <sheet name="Akt" sheetId="17" r:id="rId8"/>
     <sheet name="Pdgfb" sheetId="10" r:id="rId9"/>
-    <sheet name="ErbB" sheetId="5" r:id="rId10"/>
-    <sheet name="Ras" sheetId="6" r:id="rId11"/>
-    <sheet name="Apelin" sheetId="11" r:id="rId12"/>
-    <sheet name="JAK-STAT" sheetId="12" r:id="rId13"/>
-    <sheet name="Nfkb" sheetId="13" r:id="rId14"/>
-    <sheet name="TNF" sheetId="14" r:id="rId15"/>
-    <sheet name="Foxo" sheetId="16" r:id="rId16"/>
-    <sheet name="mTOR" sheetId="18" r:id="rId17"/>
-    <sheet name="AMPK" sheetId="19" r:id="rId18"/>
-    <sheet name="cGMP-PKG" sheetId="20" r:id="rId19"/>
-    <sheet name="Sheet1" sheetId="22" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="192">
   <si>
     <t xml:space="preserve">Molecules </t>
   </si>
@@ -1302,230 +1291,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0719F0AF-8896-3B46-A0ED-9A757096CF4D}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1D6609-BB78-534D-B9AE-B6459153E1EF}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2AFE875-2C80-1449-84C1-7B87BD2FDFAA}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C5CDFB6-5BD1-264D-A1DC-AA15037AA227}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFC75C96-A02C-5941-A5BD-7F818BFC7CC8}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{116211A4-868D-5847-9628-131EEAD7A871}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BBE504A-319E-0C48-94B0-7AD00E37C783}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F9532F8-7D23-2F4E-8CED-08A3F463F309}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8C6AF7A-DEAA-8140-8D24-C250E8F6F204}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4835A2C-D3ED-1340-9BDF-F77CE670DF3B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35B2A196-9528-444D-9B6B-30B075FBCB71}">
   <dimension ref="A1:D19"/>
@@ -1696,15 +1461,6 @@
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{BF23F103-203E-D842-89A2-7E2C939ABEFD}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEBC8247-C426-A142-8BB5-48DADB41453C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
